--- a/exports/BCA-A_Full_Report_May_2026.xlsx
+++ b/exports/BCA-A_Full_Report_May_2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Web Development" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Artificial Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -598,6 +598,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>23BCA101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tanisha Sharma</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>23BCA102</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Divanshu Garg</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
